--- a/小组赛.xlsx
+++ b/小组赛.xlsx
@@ -2616,17 +2616,17 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>苏格兰</t>
+          <t>摩洛哥</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>海地</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2658,17 +2658,17 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>摩洛哥</t>
+          <t>苏格兰</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>海地</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2700,17 +2700,17 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>捷克</t>
+          <t>南非</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>墨西哥</t>
+          <t>韩国</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2742,17 +2742,17 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>南非</t>
+          <t>捷克</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>韩国</t>
+          <t>墨西哥</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2784,17 +2784,17 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>库拉索</t>
+          <t>厄瓜多尔</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>科特迪瓦</t>
+          <t>德国</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2826,17 +2826,17 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>厄瓜多尔</t>
+          <t>库拉索</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>德国</t>
+          <t>科特迪瓦</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3036,17 +3036,17 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>塞内加尔</t>
+          <t>挪威</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>伊拉克</t>
+          <t>法国</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3078,17 +3078,17 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>挪威</t>
+          <t>塞内加尔</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>法国</t>
+          <t>伊拉克</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3288,17 +3288,17 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>克罗地亚</t>
+          <t>巴拿马</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>加纳</t>
+          <t>英格兰</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3330,17 +3330,17 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>巴拿马</t>
+          <t>克罗地亚</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>英格兰</t>
+          <t>加纳</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3372,17 +3372,17 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>哥伦比亚</t>
+          <t>刚果民主共和国</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>乌兹别克斯坦</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>刚果民主共和国</t>
+          <t>哥伦比亚</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>乌兹别克斯坦</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -3456,17 +3456,17 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>约旦</t>
+          <t>阿尔及利亚</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>3-3</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>阿根廷</t>
+          <t>奥地利</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -3498,17 +3498,17 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>阿尔及利亚</t>
+          <t>约旦</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>3-3</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>奥地利</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">

--- a/小组赛.xlsx
+++ b/小组赛.xlsx
@@ -2532,17 +2532,17 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>瑞士</t>
+          <t>波黑</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>卡塔尔</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2574,17 +2574,17 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>波黑</t>
+          <t>瑞士</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>卡塔尔</t>
+          <t>加拿大</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2700,17 +2700,17 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>南非</t>
+          <t>捷克</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>韩国</t>
+          <t>墨西哥</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2742,17 +2742,17 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>捷克</t>
+          <t>南非</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>墨西哥</t>
+          <t>韩国</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2868,17 +2868,17 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>突尼斯</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>荷兰</t>
+          <t>瑞典</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2910,17 +2910,17 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>突尼斯</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>瑞典</t>
+          <t>荷兰</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3120,17 +3120,17 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>乌拉圭</t>
+          <t>佛得角</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>沙特阿拉伯</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3162,17 +3162,17 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>佛得角</t>
+          <t>乌拉圭</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>沙特阿拉伯</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3204,17 +3204,17 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>新西兰</t>
+          <t>埃及</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>比利时</t>
+          <t>伊朗</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3246,17 +3246,17 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>埃及</t>
+          <t>新西兰</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>伊朗</t>
+          <t>比利时</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">

--- a/小组赛.xlsx
+++ b/小组赛.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>06/12</t>
+          <t>06/13</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -511,22 +511,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>A组</t>
+          <t>B组</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>墨西哥</t>
+          <t>加拿大</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>南非</t>
+          <t>波黑</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -538,7 +538,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>06/12</t>
+          <t>06/13</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -548,27 +548,27 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>A组</t>
+          <t>D组</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>韩国</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>捷克</t>
+          <t>巴拉圭</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -580,7 +580,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>06/13</t>
+          <t>06/14</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>卡塔尔</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>波黑</t>
+          <t>瑞士</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>06/13</t>
+          <t>06/14</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -632,27 +632,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>D组</t>
+          <t>C组</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>巴拉圭</t>
+          <t>摩洛哥</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -674,27 +674,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>B组</t>
+          <t>C组</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>卡塔尔</t>
+          <t>海地</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>瑞士</t>
+          <t>苏格兰</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -716,27 +716,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>C组</t>
+          <t>D组</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>澳大利亚</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>摩洛哥</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>06/14</t>
+          <t>06/15</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -758,27 +758,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>C组</t>
+          <t>E组</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>海地</t>
+          <t>德国</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>7-1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>苏格兰</t>
+          <t>库拉索</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>06/14</t>
+          <t>06/15</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -800,27 +800,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>D组</t>
+          <t>F组</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>荷兰</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -852,17 +852,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>德国</t>
+          <t>科特迪瓦</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>库拉索</t>
+          <t>厄瓜多尔</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -894,17 +894,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>荷兰</t>
+          <t>瑞典</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>突尼斯</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>06/15</t>
+          <t>06/16</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -926,27 +926,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>E组</t>
+          <t>H组</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>科特迪瓦</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>厄瓜多尔</t>
+          <t>佛得角</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -958,7 +958,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>06/15</t>
+          <t>06/16</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -968,27 +968,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>F组</t>
+          <t>G组</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>瑞典</t>
+          <t>比利时</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>突尼斯</t>
+          <t>埃及</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1020,17 +1020,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>沙特阿拉伯</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>佛得角</t>
+          <t>乌拉圭</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1062,17 +1062,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>比利时</t>
+          <t>伊朗</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>埃及</t>
+          <t>新西兰</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>06/16</t>
+          <t>06/17</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1094,27 +1094,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>H组</t>
+          <t>I组</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>沙特阿拉伯</t>
+          <t>法国</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>乌拉圭</t>
+          <t>塞内加尔</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>06/16</t>
+          <t>06/17</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1136,27 +1136,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>G组</t>
+          <t>I组</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>伊朗</t>
+          <t>伊拉克</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>新西兰</t>
+          <t>挪威</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1178,27 +1178,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>I组</t>
+          <t>J组</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>法国</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>塞内加尔</t>
+          <t>阿尔及利亚</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1220,27 +1220,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>I组</t>
+          <t>J组</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>伊拉克</t>
+          <t>奥地利</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>挪威</t>
+          <t>约旦</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/17</t>
+          <t>06/18</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1262,27 +1262,27 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>J组</t>
+          <t>K组</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>阿根廷</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>阿尔及利亚</t>
+          <t>刚果民主共和国</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/17</t>
+          <t>06/18</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1304,27 +1304,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>J组</t>
+          <t>L组</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>奥地利</t>
+          <t>英格兰</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>约旦</t>
+          <t>克罗地亚</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1346,27 +1346,27 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>K组</t>
+          <t>L组</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>加纳</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>刚果民主共和国</t>
+          <t>巴拿马</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1388,27 +1388,27 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>L组</t>
+          <t>K组</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>英格兰</t>
+          <t>乌兹别克斯坦</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>克罗地亚</t>
+          <t>哥伦比亚</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1420,37 +1420,37 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>06/18</t>
+          <t>06/19</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>第一轮</t>
+          <t>第二轮</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>L组</t>
+          <t>A组</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>加纳</t>
+          <t>捷克</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>巴拿马</t>
+          <t>南非</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1462,37 +1462,37 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>06/18</t>
+          <t>06/19</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>第一轮</t>
+          <t>第二轮</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>K组</t>
+          <t>B组</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>乌兹别克斯坦</t>
+          <t>瑞士</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>哥伦比亚</t>
+          <t>波黑</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1514,27 +1514,27 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>A组</t>
+          <t>B组</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>捷克</t>
+          <t>加拿大</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>6-0</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>南非</t>
+          <t>卡塔尔</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1556,27 +1556,27 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>B组</t>
+          <t>A组</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>瑞士</t>
+          <t>墨西哥</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>波黑</t>
+          <t>韩国</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1588,7 +1588,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/19</t>
+          <t>06/20</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1598,27 +1598,27 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>B组</t>
+          <t>D组</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>卡塔尔</t>
+          <t>澳大利亚</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/19</t>
+          <t>06/20</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1640,27 +1640,27 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>A组</t>
+          <t>C组</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>墨西哥</t>
+          <t>苏格兰</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>韩国</t>
+          <t>摩洛哥</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1682,27 +1682,27 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>D组</t>
+          <t>C组</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>海地</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1724,17 +1724,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>C组</t>
+          <t>D组</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>苏格兰</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>摩洛哥</t>
+          <t>巴拉圭</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/20</t>
+          <t>06/21</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1766,27 +1766,27 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>C组</t>
+          <t>F组</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>荷兰</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>海地</t>
+          <t>瑞典</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/20</t>
+          <t>06/21</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1808,27 +1808,27 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>D组</t>
+          <t>E组</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>德国</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>巴拉圭</t>
+          <t>科特迪瓦</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1850,27 +1850,27 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>F组</t>
+          <t>E组</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>荷兰</t>
+          <t>厄瓜多尔</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>瑞典</t>
+          <t>库拉索</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1892,27 +1892,27 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>E组</t>
+          <t>F组</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>德国</t>
+          <t>突尼斯</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>0-4</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>科特迪瓦</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>06/21</t>
+          <t>06/22</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1934,27 +1934,27 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>E组</t>
+          <t>H组</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>厄瓜多尔</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>库拉索</t>
+          <t>沙特阿拉伯</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>06/21</t>
+          <t>06/22</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -1976,27 +1976,27 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>F组</t>
+          <t>G组</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>突尼斯</t>
+          <t>比利时</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0-4</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>伊朗</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2028,17 +2028,17 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>乌拉圭</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>沙特阿拉伯</t>
+          <t>佛得角</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2070,17 +2070,17 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>比利时</t>
+          <t>新西兰</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>伊朗</t>
+          <t>埃及</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2092,7 +2092,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>06/22</t>
+          <t>06/23</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2102,27 +2102,27 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>H组</t>
+          <t>J组</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>乌拉圭</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>佛得角</t>
+          <t>奥地利</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>06/22</t>
+          <t>06/23</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2144,27 +2144,27 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>G组</t>
+          <t>I组</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>新西兰</t>
+          <t>法国</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>埃及</t>
+          <t>伊拉克</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2186,27 +2186,27 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>J组</t>
+          <t>I组</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>阿根廷</t>
+          <t>挪威</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>奥地利</t>
+          <t>塞内加尔</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2228,27 +2228,27 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>I组</t>
+          <t>J组</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>法国</t>
+          <t>约旦</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>伊拉克</t>
+          <t>阿尔及利亚</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2260,7 +2260,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>06/23</t>
+          <t>06/24</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2270,27 +2270,27 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>I组</t>
+          <t>K组</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>挪威</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>塞内加尔</t>
+          <t>乌兹别克斯坦</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>06/23</t>
+          <t>06/24</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2312,27 +2312,27 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>J组</t>
+          <t>L组</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>约旦</t>
+          <t>英格兰</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>阿尔及利亚</t>
+          <t>加纳</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2354,27 +2354,27 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>K组</t>
+          <t>L组</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>巴拿马</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>乌兹别克斯坦</t>
+          <t>克罗地亚</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2396,27 +2396,27 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>L组</t>
+          <t>K组</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>英格兰</t>
+          <t>哥伦比亚</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>加纳</t>
+          <t>刚果民主共和国</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2428,37 +2428,37 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>06/24</t>
+          <t>06/25</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>第二轮</t>
+          <t>第三轮</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>L组</t>
+          <t>B组</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>巴拿马</t>
+          <t>瑞士</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>克罗地亚</t>
+          <t>加拿大</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2470,37 +2470,37 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>06/24</t>
+          <t>06/25</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>第二轮</t>
+          <t>第三轮</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>K组</t>
+          <t>B组</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>哥伦比亚</t>
+          <t>波黑</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>刚果民主共和国</t>
+          <t>卡塔尔</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2522,27 +2522,27 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>B组</t>
+          <t>C组</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>波黑</t>
+          <t>苏格兰</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>卡塔尔</t>
+          <t>巴西</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2564,27 +2564,27 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>B组</t>
+          <t>C组</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>瑞士</t>
+          <t>摩洛哥</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>加拿大</t>
+          <t>海地</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2606,27 +2606,27 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>C组</t>
+          <t>A组</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>摩洛哥</t>
+          <t>捷克</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>海地</t>
+          <t>墨西哥</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2648,27 +2648,27 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>C组</t>
+          <t>A组</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>苏格兰</t>
+          <t>南非</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>巴西</t>
+          <t>韩国</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>06/25</t>
+          <t>06/26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2690,27 +2690,27 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>A组</t>
+          <t>E组</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>捷克</t>
+          <t>厄瓜多尔</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>0-3</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>墨西哥</t>
+          <t>德国</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>06/25</t>
+          <t>06/26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2732,27 +2732,27 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>A组</t>
+          <t>E组</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>南非</t>
+          <t>库拉索</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>韩国</t>
+          <t>科特迪瓦</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2774,27 +2774,27 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>E组</t>
+          <t>F组</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>厄瓜多尔</t>
+          <t>突尼斯</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>德国</t>
+          <t>荷兰</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2816,27 +2816,27 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>E组</t>
+          <t>F组</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>库拉索</t>
+          <t>日本</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>科特迪瓦</t>
+          <t>瑞典</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2858,27 +2858,27 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>F组</t>
+          <t>D组</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>日本</t>
+          <t>巴拉圭</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>瑞典</t>
+          <t>澳大利亚</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2900,27 +2900,27 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>F组</t>
+          <t>D组</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>突尼斯</t>
+          <t>土耳其</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>荷兰</t>
+          <t>美国</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -2932,7 +2932,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>06/26</t>
+          <t>06/27</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -2942,27 +2942,27 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>D组</t>
+          <t>I组</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>巴拉圭</t>
+          <t>挪威</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>澳大利亚</t>
+          <t>法国</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>06/26</t>
+          <t>06/27</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -2984,27 +2984,27 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>D组</t>
+          <t>I组</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>土耳其</t>
+          <t>塞内加尔</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>伊拉克</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3026,27 +3026,27 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>I组</t>
+          <t>H组</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>挪威</t>
+          <t>佛得角</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>法国</t>
+          <t>沙特阿拉伯</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3068,27 +3068,27 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>I组</t>
+          <t>H组</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>塞内加尔</t>
+          <t>乌拉圭</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>伊拉克</t>
+          <t>西班牙</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3110,27 +3110,27 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>H组</t>
+          <t>G组</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>佛得角</t>
+          <t>新西兰</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>沙特阿拉伯</t>
+          <t>比利时</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3152,27 +3152,27 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>H组</t>
+          <t>G组</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>乌拉圭</t>
+          <t>埃及</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>西班牙</t>
+          <t>伊朗</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/27</t>
+          <t>06/28</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3194,27 +3194,27 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>G组</t>
+          <t>L组</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>埃及</t>
+          <t>巴拿马</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>伊朗</t>
+          <t>英格兰</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/27</t>
+          <t>06/28</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3236,27 +3236,27 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>G组</t>
+          <t>L组</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>新西兰</t>
+          <t>克罗地亚</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>比利时</t>
+          <t>加纳</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3278,27 +3278,27 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>L组</t>
+          <t>K组</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>巴拿马</t>
+          <t>刚果民主共和国</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>英格兰</t>
+          <t>乌兹别克斯坦</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3320,27 +3320,27 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>L组</t>
+          <t>K组</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>克罗地亚</t>
+          <t>哥伦比亚</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>加纳</t>
+          <t>葡萄牙</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3362,27 +3362,27 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>K组</t>
+          <t>J组</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>刚果民主共和国</t>
+          <t>约旦</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>乌兹别克斯坦</t>
+          <t>阿根廷</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3404,114 +3404,30 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>K组</t>
+          <t>J组</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>哥伦比亚</t>
+          <t>阿尔及利亚</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>3-3</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>葡萄牙</t>
+          <t>奥地利</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>已结束</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>06/28</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>第三轮</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>J组</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>阿尔及利亚</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>3-3</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>奥地利</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>已结束</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>06/28</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>第三轮</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>J组</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>约旦</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>1-3</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>阿根廷</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>已结束</t>
         </is>
